--- a/src/data/episodes/4.xlsx
+++ b/src/data/episodes/4.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>الحلقة</t>
   </si>
@@ -31,10 +31,22 @@
     <t>باب</t>
   </si>
   <si>
+    <t>00:00</t>
+  </si>
+  <si>
     <t>الحديث / الأثر</t>
   </si>
   <si>
+    <t>08:20</t>
+  </si>
+  <si>
     <t>اعلام</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>السفور</t>
   </si>
   <si>
     <t>تعاريف</t>
@@ -79,7 +91,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -102,11 +114,18 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -122,6 +141,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -469,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="17.714285714285715" customWidth="1"/>
@@ -479,7 +501,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1">
+        <v>4</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -517,37 +541,45 @@
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+      <c r="A5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="6">
+        <v>3</v>
+      </c>
       <c r="C5" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="7">
+        <v>4</v>
+      </c>
+      <c r="C6" s="6"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
+      <c r="A7" s="8"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -556,36 +588,38 @@
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
@@ -596,9 +630,17 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
